--- a/samples/SanLuong-khach-mau.xlsx
+++ b/samples/SanLuong-khach-mau.xlsx
@@ -3,11 +3,16 @@
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:workbookPr codeName="ThisWorkbook"/>
   <x:bookViews>
-    <x:workbookView firstSheet="0" activeTab="1"/>
+    <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <x:sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <x:sheet name="Chuyền 1" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Chuyền 2" sheetId="2" r:id="rId3"/>
+    <x:sheet name="Chuyền 3" sheetId="3" r:id="rId4"/>
+    <x:sheet name="Chuyền 4" sheetId="4" r:id="rId5"/>
+    <x:sheet name="Chuyền 5" sheetId="5" r:id="rId6"/>
+    <x:sheet name="Chuyền 6" sheetId="6" r:id="rId7"/>
+    <x:sheet name="Cũ" sheetId="7" r:id="rId8"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -17,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
-    <x:t>日期：2026/09/29
+    <x:t>日期：2026/09/30
 NGÀY THÁNG</x:t>
   </x:si>
   <x:si>
@@ -67,11 +72,11 @@
     <x:t>BAO TAY XANH</x:t>
   </x:si>
   <x:si>
-    <x:t>日期：2026/09/30
-NGÀY THÁNG</x:t>
+    <x:t>GĂNG TAY TRẮNG</x:t>
   </x:si>
   <x:si>
-    <x:t>GĂNG TAY TRẮNG</x:t>
+    <x:t>日期：2026/09/29
+NGÀY THÁNG</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -470,7 +475,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K10"/>
+  <x:dimension ref="A1:K7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -528,7 +533,7 @@
         <x:f>B3*C3</x:f>
       </x:c>
       <x:c r="E3" s="4">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F3" s="5">
         <x:f>+E3/D3</x:f>
@@ -561,7 +566,7 @@
         <x:f>B4*C4</x:f>
       </x:c>
       <x:c r="E4" s="4">
-        <x:v>900</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="F4" s="5">
         <x:f>+E4/D4</x:f>
@@ -594,7 +599,7 @@
         <x:f>B5*C5</x:f>
       </x:c>
       <x:c r="E5" s="4">
-        <x:v>1665</x:v>
+        <x:v>1850</x:v>
       </x:c>
       <x:c r="F5" s="5">
         <x:f>+E5/D5</x:f>
@@ -614,129 +619,30 @@
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="3">
-        <x:v>700</x:v>
-      </x:c>
-      <x:c r="B6" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="3">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D6" s="4">
-        <x:f>B6*C6</x:f>
-      </x:c>
-      <x:c r="E6" s="4">
-        <x:v>1665</x:v>
-      </x:c>
-      <x:c r="F6" s="5">
-        <x:f>+E6/D6</x:f>
-      </x:c>
-      <x:c r="G6" s="4">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H6" s="4">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="I6" s="4">
-        <x:f>+H6-G6</x:f>
-      </x:c>
-      <x:c r="J6" s="5">
-        <x:f>+H6/G6</x:f>
-      </x:c>
+      <x:c r="A6" s="3"/>
+      <x:c r="B6" s="3"/>
+      <x:c r="C6" s="3"/>
+      <x:c r="D6" s="3"/>
+      <x:c r="E6" s="3"/>
+      <x:c r="F6" s="3"/>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="3"/>
+      <x:c r="I6" s="3"/>
+      <x:c r="J6" s="3"/>
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="A7" s="3">
-        <x:v>972</x:v>
-      </x:c>
-      <x:c r="B7" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="3">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D7" s="4">
-        <x:f>B7*C7</x:f>
-      </x:c>
-      <x:c r="E7" s="4">
-        <x:v>1800</x:v>
-      </x:c>
-      <x:c r="F7" s="5">
-        <x:f>+E7/D7</x:f>
-      </x:c>
-      <x:c r="G7" s="4">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H7" s="4">
-        <x:v>55000</x:v>
-      </x:c>
-      <x:c r="I7" s="4">
-        <x:f>+H7-G7</x:f>
-      </x:c>
-      <x:c r="J7" s="5">
-        <x:f>+H7/G7</x:f>
-      </x:c>
+      <x:c r="A7" s="3"/>
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3"/>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3"/>
+      <x:c r="F7" s="3"/>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
       <x:c r="K7" s="3"/>
-    </x:row>
-    <x:row r="8" spans="1:11">
-      <x:c r="A8" s="3">
-        <x:v>959</x:v>
-      </x:c>
-      <x:c r="B8" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="3">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D8" s="4">
-        <x:f>B8*C8</x:f>
-      </x:c>
-      <x:c r="E8" s="4">
-        <x:v>1665</x:v>
-      </x:c>
-      <x:c r="F8" s="5">
-        <x:f>+E8/D8</x:f>
-      </x:c>
-      <x:c r="G8" s="4">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H8" s="4">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="I8" s="4">
-        <x:f>+H8-G8</x:f>
-      </x:c>
-      <x:c r="J8" s="5">
-        <x:f>+H8/G8</x:f>
-      </x:c>
-      <x:c r="K8" s="3"/>
-    </x:row>
-    <x:row r="9" spans="1:11">
-      <x:c r="A9" s="3"/>
-      <x:c r="B9" s="3"/>
-      <x:c r="C9" s="3"/>
-      <x:c r="D9" s="3"/>
-      <x:c r="E9" s="3"/>
-      <x:c r="F9" s="3"/>
-      <x:c r="G9" s="3"/>
-      <x:c r="H9" s="3"/>
-      <x:c r="I9" s="3"/>
-      <x:c r="J9" s="3"/>
-      <x:c r="K9" s="3"/>
-    </x:row>
-    <x:row r="10" spans="1:11">
-      <x:c r="A10" s="3"/>
-      <x:c r="B10" s="3"/>
-      <x:c r="C10" s="3"/>
-      <x:c r="D10" s="3"/>
-      <x:c r="E10" s="3"/>
-      <x:c r="F10" s="3"/>
-      <x:c r="G10" s="3"/>
-      <x:c r="H10" s="3"/>
-      <x:c r="I10" s="3"/>
-      <x:c r="J10" s="3"/>
-      <x:c r="K10" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
@@ -755,7 +661,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K15"/>
+  <x:dimension ref="A1:K7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -763,7 +669,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
@@ -800,6 +706,1134 @@
       <x:c r="K2" s="3"/>
     </x:row>
     <x:row r="3" spans="1:11">
+      <x:c r="A3" s="3">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="B3" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D3" s="4">
+        <x:f>B3*C3</x:f>
+      </x:c>
+      <x:c r="E3" s="4">
+        <x:v>1850</x:v>
+      </x:c>
+      <x:c r="F3" s="5">
+        <x:f>+E3/D3</x:f>
+      </x:c>
+      <x:c r="G3" s="4">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H3" s="4">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="I3" s="4">
+        <x:f>+H3-G3</x:f>
+      </x:c>
+      <x:c r="J3" s="5">
+        <x:f>+H3/G3</x:f>
+      </x:c>
+      <x:c r="K3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="3">
+        <x:v>972</x:v>
+      </x:c>
+      <x:c r="B4" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="3">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D4" s="4">
+        <x:f>B4*C4</x:f>
+      </x:c>
+      <x:c r="E4" s="4">
+        <x:v>2000</x:v>
+      </x:c>
+      <x:c r="F4" s="5">
+        <x:f>+E4/D4</x:f>
+      </x:c>
+      <x:c r="G4" s="4">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
+        <x:v>55000</x:v>
+      </x:c>
+      <x:c r="I4" s="4">
+        <x:f>+H4-G4</x:f>
+      </x:c>
+      <x:c r="J4" s="5">
+        <x:f>+H4/G4</x:f>
+      </x:c>
+      <x:c r="K4" s="3"/>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="3">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="B5" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C5" s="3">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D5" s="4">
+        <x:f>B5*C5</x:f>
+      </x:c>
+      <x:c r="E5" s="4">
+        <x:v>1850</x:v>
+      </x:c>
+      <x:c r="F5" s="5">
+        <x:f>+E5/D5</x:f>
+      </x:c>
+      <x:c r="G5" s="4">
+        <x:v>50000</x:v>
+      </x:c>
+      <x:c r="H5" s="4">
+        <x:v>45000</x:v>
+      </x:c>
+      <x:c r="I5" s="4">
+        <x:f>+H5-G5</x:f>
+      </x:c>
+      <x:c r="J5" s="5">
+        <x:f>+H5/G5</x:f>
+      </x:c>
+      <x:c r="K5" s="3"/>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="3"/>
+      <x:c r="B6" s="3"/>
+      <x:c r="C6" s="3"/>
+      <x:c r="D6" s="3"/>
+      <x:c r="E6" s="3"/>
+      <x:c r="F6" s="3"/>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="3"/>
+      <x:c r="I6" s="3"/>
+      <x:c r="J6" s="3"/>
+      <x:c r="K6" s="3"/>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="3"/>
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3"/>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3"/>
+      <x:c r="F7" s="3"/>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="1">
+    <x:mergeCell ref="A1:B1"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K8"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="3"/>
+    </x:row>
+    <x:row r="3" spans="1:11">
+      <x:c r="A3" s="3">
+        <x:v>1201</x:v>
+      </x:c>
+      <x:c r="B3" s="3">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D3" s="4">
+        <x:f>B3*C3</x:f>
+      </x:c>
+      <x:c r="E3" s="4">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="F3" s="5">
+        <x:f>+E3/D3</x:f>
+      </x:c>
+      <x:c r="G3" s="4">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="H3" s="4">
+        <x:v>24500</x:v>
+      </x:c>
+      <x:c r="I3" s="4">
+        <x:f>+H3-G3</x:f>
+      </x:c>
+      <x:c r="J3" s="5">
+        <x:f>+H3/G3</x:f>
+      </x:c>
+      <x:c r="K3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="3">
+        <x:v>1305</x:v>
+      </x:c>
+      <x:c r="B4" s="3">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="3">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D4" s="4">
+        <x:f>B4*C4</x:f>
+      </x:c>
+      <x:c r="E4" s="4">
+        <x:v>1150</x:v>
+      </x:c>
+      <x:c r="F4" s="5">
+        <x:f>+E4/D4</x:f>
+      </x:c>
+      <x:c r="G4" s="4">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
+        <x:v>28800</x:v>
+      </x:c>
+      <x:c r="I4" s="4">
+        <x:f>+H4-G4</x:f>
+      </x:c>
+      <x:c r="J4" s="5">
+        <x:f>+H4/G4</x:f>
+      </x:c>
+      <x:c r="K4" s="3"/>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="3">
+        <x:v>1306</x:v>
+      </x:c>
+      <x:c r="B5" s="3">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="3">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D5" s="4">
+        <x:f>B5*C5</x:f>
+      </x:c>
+      <x:c r="E5" s="4">
+        <x:v>1180</x:v>
+      </x:c>
+      <x:c r="F5" s="5">
+        <x:f>+E5/D5</x:f>
+      </x:c>
+      <x:c r="G5" s="4">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="H5" s="4">
+        <x:v>29900</x:v>
+      </x:c>
+      <x:c r="I5" s="4">
+        <x:f>+H5-G5</x:f>
+      </x:c>
+      <x:c r="J5" s="5">
+        <x:f>+H5/G5</x:f>
+      </x:c>
+      <x:c r="K5" s="3"/>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="3">
+        <x:v>1310</x:v>
+      </x:c>
+      <x:c r="B6" s="3">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C6" s="3">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D6" s="4">
+        <x:f>B6*C6</x:f>
+      </x:c>
+      <x:c r="E6" s="4">
+        <x:v>1090</x:v>
+      </x:c>
+      <x:c r="F6" s="5">
+        <x:f>+E6/D6</x:f>
+      </x:c>
+      <x:c r="G6" s="4">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="H6" s="4">
+        <x:v>27100</x:v>
+      </x:c>
+      <x:c r="I6" s="4">
+        <x:f>+H6-G6</x:f>
+      </x:c>
+      <x:c r="J6" s="5">
+        <x:f>+H6/G6</x:f>
+      </x:c>
+      <x:c r="K6" s="3"/>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="3"/>
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3"/>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3"/>
+      <x:c r="F7" s="3"/>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="3"/>
+      <x:c r="B8" s="3"/>
+      <x:c r="C8" s="3"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="1">
+    <x:mergeCell ref="A1:B1"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K7"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="3"/>
+    </x:row>
+    <x:row r="3" spans="1:11">
+      <x:c r="A3" s="3" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D3" s="4">
+        <x:f>B3*C3</x:f>
+      </x:c>
+      <x:c r="E3" s="4">
+        <x:v>1310</x:v>
+      </x:c>
+      <x:c r="F3" s="5">
+        <x:f>+E3/D3</x:f>
+      </x:c>
+      <x:c r="G3" s="4">
+        <x:v>36000</x:v>
+      </x:c>
+      <x:c r="H3" s="4">
+        <x:v>36500</x:v>
+      </x:c>
+      <x:c r="I3" s="4">
+        <x:f>+H3-G3</x:f>
+      </x:c>
+      <x:c r="J3" s="5">
+        <x:f>+H3/G3</x:f>
+      </x:c>
+      <x:c r="K3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="3">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="B4" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="3">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D4" s="4">
+        <x:f>B4*C4</x:f>
+      </x:c>
+      <x:c r="E4" s="4">
+        <x:v>1700</x:v>
+      </x:c>
+      <x:c r="F4" s="5">
+        <x:f>+E4/D4</x:f>
+      </x:c>
+      <x:c r="G4" s="4">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
+        <x:v>51000</x:v>
+      </x:c>
+      <x:c r="I4" s="4">
+        <x:f>+H4-G4</x:f>
+      </x:c>
+      <x:c r="J4" s="5">
+        <x:f>+H4/G4</x:f>
+      </x:c>
+      <x:c r="K4" s="3"/>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="3">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="B5" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C5" s="3">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="D5" s="4">
+        <x:f>B5*C5</x:f>
+      </x:c>
+      <x:c r="E5" s="4">
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="F5" s="5">
+        <x:f>+E5/D5</x:f>
+      </x:c>
+      <x:c r="G5" s="4">
+        <x:v>60000</x:v>
+      </x:c>
+      <x:c r="H5" s="4">
+        <x:v>61200</x:v>
+      </x:c>
+      <x:c r="I5" s="4">
+        <x:f>+H5-G5</x:f>
+      </x:c>
+      <x:c r="J5" s="5">
+        <x:f>+H5/G5</x:f>
+      </x:c>
+      <x:c r="K5" s="3"/>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="3"/>
+      <x:c r="B6" s="3"/>
+      <x:c r="C6" s="3"/>
+      <x:c r="D6" s="3"/>
+      <x:c r="E6" s="3"/>
+      <x:c r="F6" s="3"/>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="3"/>
+      <x:c r="I6" s="3"/>
+      <x:c r="J6" s="3"/>
+      <x:c r="K6" s="3"/>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="3"/>
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3"/>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3"/>
+      <x:c r="F7" s="3"/>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="1">
+    <x:mergeCell ref="A1:B1"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K8"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="3"/>
+    </x:row>
+    <x:row r="3" spans="1:11">
+      <x:c r="A3" s="3">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="B3" s="3">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D3" s="4">
+        <x:f>B3*C3</x:f>
+      </x:c>
+      <x:c r="E3" s="4">
+        <x:v>1500</x:v>
+      </x:c>
+      <x:c r="F3" s="5">
+        <x:f>+E3/D3</x:f>
+      </x:c>
+      <x:c r="G3" s="4">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="H3" s="4">
+        <x:v>40100</x:v>
+      </x:c>
+      <x:c r="I3" s="4">
+        <x:f>+H3-G3</x:f>
+      </x:c>
+      <x:c r="J3" s="5">
+        <x:f>+H3/G3</x:f>
+      </x:c>
+      <x:c r="K3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="3">
+        <x:v>516</x:v>
+      </x:c>
+      <x:c r="B4" s="3">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C4" s="3">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D4" s="4">
+        <x:f>B4*C4</x:f>
+      </x:c>
+      <x:c r="E4" s="4">
+        <x:v>1390</x:v>
+      </x:c>
+      <x:c r="F4" s="5">
+        <x:f>+E4/D4</x:f>
+      </x:c>
+      <x:c r="G4" s="4">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
+        <x:v>37800</x:v>
+      </x:c>
+      <x:c r="I4" s="4">
+        <x:f>+H4-G4</x:f>
+      </x:c>
+      <x:c r="J4" s="5">
+        <x:f>+H4/G4</x:f>
+      </x:c>
+      <x:c r="K4" s="3"/>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="3">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B5" s="3">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C5" s="3">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D5" s="4">
+        <x:f>B5*C5</x:f>
+      </x:c>
+      <x:c r="E5" s="4">
+        <x:v>1440</x:v>
+      </x:c>
+      <x:c r="F5" s="5">
+        <x:f>+E5/D5</x:f>
+      </x:c>
+      <x:c r="G5" s="4">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="H5" s="4">
+        <x:v>41500</x:v>
+      </x:c>
+      <x:c r="I5" s="4">
+        <x:f>+H5-G5</x:f>
+      </x:c>
+      <x:c r="J5" s="5">
+        <x:f>+H5/G5</x:f>
+      </x:c>
+      <x:c r="K5" s="3"/>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="3">
+        <x:v>883</x:v>
+      </x:c>
+      <x:c r="B6" s="3">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C6" s="3">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="D6" s="4">
+        <x:f>B6*C6</x:f>
+      </x:c>
+      <x:c r="E6" s="4">
+        <x:v>1460</x:v>
+      </x:c>
+      <x:c r="F6" s="5">
+        <x:f>+E6/D6</x:f>
+      </x:c>
+      <x:c r="G6" s="4">
+        <x:v>42000</x:v>
+      </x:c>
+      <x:c r="H6" s="4">
+        <x:v>40900</x:v>
+      </x:c>
+      <x:c r="I6" s="4">
+        <x:f>+H6-G6</x:f>
+      </x:c>
+      <x:c r="J6" s="5">
+        <x:f>+H6/G6</x:f>
+      </x:c>
+      <x:c r="K6" s="3"/>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="3"/>
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3"/>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3"/>
+      <x:c r="F7" s="3"/>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
+      <x:c r="K7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="3"/>
+      <x:c r="B8" s="3"/>
+      <x:c r="C8" s="3"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="1">
+    <x:mergeCell ref="A1:B1"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K11"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11">
+      <x:c r="A1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="3"/>
+    </x:row>
+    <x:row r="3" spans="1:11">
+      <x:c r="A3" s="3">
+        <x:v>730</x:v>
+      </x:c>
+      <x:c r="B3" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="3">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D3" s="4">
+        <x:f>B3*C3</x:f>
+      </x:c>
+      <x:c r="E3" s="4">
+        <x:v>1810</x:v>
+      </x:c>
+      <x:c r="F3" s="5">
+        <x:f>+E3/D3</x:f>
+      </x:c>
+      <x:c r="G3" s="4">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="H3" s="4">
+        <x:v>50400</x:v>
+      </x:c>
+      <x:c r="I3" s="4">
+        <x:f>+H3-G3</x:f>
+      </x:c>
+      <x:c r="J3" s="5">
+        <x:f>+H3/G3</x:f>
+      </x:c>
+      <x:c r="K3" s="3"/>
+    </x:row>
+    <x:row r="4" spans="1:11">
+      <x:c r="A4" s="3">
+        <x:v>731</x:v>
+      </x:c>
+      <x:c r="B4" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="3">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D4" s="4">
+        <x:f>B4*C4</x:f>
+      </x:c>
+      <x:c r="E4" s="4">
+        <x:v>1620</x:v>
+      </x:c>
+      <x:c r="F4" s="5">
+        <x:f>+E4/D4</x:f>
+      </x:c>
+      <x:c r="G4" s="4">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
+        <x:v>46800</x:v>
+      </x:c>
+      <x:c r="I4" s="4">
+        <x:f>+H4-G4</x:f>
+      </x:c>
+      <x:c r="J4" s="5">
+        <x:f>+H4/G4</x:f>
+      </x:c>
+      <x:c r="K4" s="3"/>
+    </x:row>
+    <x:row r="5" spans="1:11">
+      <x:c r="A5" s="3">
+        <x:v>735</x:v>
+      </x:c>
+      <x:c r="B5" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C5" s="3">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D5" s="4">
+        <x:f>B5*C5</x:f>
+      </x:c>
+      <x:c r="E5" s="4">
+        <x:v>1790</x:v>
+      </x:c>
+      <x:c r="F5" s="5">
+        <x:f>+E5/D5</x:f>
+      </x:c>
+      <x:c r="G5" s="4">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="H5" s="4">
+        <x:v>51900</x:v>
+      </x:c>
+      <x:c r="I5" s="4">
+        <x:f>+H5-G5</x:f>
+      </x:c>
+      <x:c r="J5" s="5">
+        <x:f>+H5/G5</x:f>
+      </x:c>
+      <x:c r="K5" s="3"/>
+    </x:row>
+    <x:row r="6" spans="1:11">
+      <x:c r="A6" s="3">
+        <x:v>740</x:v>
+      </x:c>
+      <x:c r="B6" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="3">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D6" s="4">
+        <x:f>B6*C6</x:f>
+      </x:c>
+      <x:c r="E6" s="4">
+        <x:v>1400</x:v>
+      </x:c>
+      <x:c r="F6" s="5">
+        <x:f>+E6/D6</x:f>
+      </x:c>
+      <x:c r="G6" s="4">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="H6" s="4">
+        <x:v>43000</x:v>
+      </x:c>
+      <x:c r="I6" s="4">
+        <x:f>+H6-G6</x:f>
+      </x:c>
+      <x:c r="J6" s="5">
+        <x:f>+H6/G6</x:f>
+      </x:c>
+      <x:c r="K6" s="3"/>
+    </x:row>
+    <x:row r="7" spans="1:11">
+      <x:c r="A7" s="3">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="B7" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C7" s="3">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D7" s="4">
+        <x:f>B7*C7</x:f>
+      </x:c>
+      <x:c r="E7" s="4">
+        <x:v>1850</x:v>
+      </x:c>
+      <x:c r="F7" s="5">
+        <x:f>+E7/D7</x:f>
+      </x:c>
+      <x:c r="G7" s="4">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="H7" s="4">
+        <x:v>52800</x:v>
+      </x:c>
+      <x:c r="I7" s="4">
+        <x:f>+H7-G7</x:f>
+      </x:c>
+      <x:c r="J7" s="5">
+        <x:f>+H7/G7</x:f>
+      </x:c>
+      <x:c r="K7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="3">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="B8" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C8" s="3">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D8" s="4">
+        <x:f>B8*C8</x:f>
+      </x:c>
+      <x:c r="E8" s="4">
+        <x:v>1705</x:v>
+      </x:c>
+      <x:c r="F8" s="5">
+        <x:f>+E8/D8</x:f>
+      </x:c>
+      <x:c r="G8" s="4">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="H8" s="4">
+        <x:v>49600</x:v>
+      </x:c>
+      <x:c r="I8" s="4">
+        <x:f>+H8-G8</x:f>
+      </x:c>
+      <x:c r="J8" s="5">
+        <x:f>+H8/G8</x:f>
+      </x:c>
+      <x:c r="K8" s="3"/>
+    </x:row>
+    <x:row r="9" spans="1:11">
+      <x:c r="A9" s="3">
+        <x:v>755</x:v>
+      </x:c>
+      <x:c r="B9" s="3">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C9" s="3">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="D9" s="4">
+        <x:f>B9*C9</x:f>
+      </x:c>
+      <x:c r="E9" s="4">
+        <x:v>1830</x:v>
+      </x:c>
+      <x:c r="F9" s="5">
+        <x:f>+E9/D9</x:f>
+      </x:c>
+      <x:c r="G9" s="4">
+        <x:v>52000</x:v>
+      </x:c>
+      <x:c r="H9" s="4">
+        <x:v>50800</x:v>
+      </x:c>
+      <x:c r="I9" s="4">
+        <x:f>+H9-G9</x:f>
+      </x:c>
+      <x:c r="J9" s="5">
+        <x:f>+H9/G9</x:f>
+      </x:c>
+      <x:c r="K9" s="3"/>
+    </x:row>
+    <x:row r="10" spans="1:11">
+      <x:c r="A10" s="3"/>
+      <x:c r="B10" s="3"/>
+      <x:c r="C10" s="3"/>
+      <x:c r="D10" s="3"/>
+      <x:c r="E10" s="3"/>
+      <x:c r="F10" s="3"/>
+      <x:c r="G10" s="3"/>
+      <x:c r="H10" s="3"/>
+      <x:c r="I10" s="3"/>
+      <x:c r="J10" s="3"/>
+      <x:c r="K10" s="3"/>
+    </x:row>
+    <x:row r="11" spans="1:11">
+      <x:c r="A11" s="3"/>
+      <x:c r="B11" s="3"/>
+      <x:c r="C11" s="3"/>
+      <x:c r="D11" s="3"/>
+      <x:c r="E11" s="3"/>
+      <x:c r="F11" s="3"/>
+      <x:c r="G11" s="3"/>
+      <x:c r="H11" s="3"/>
+      <x:c r="I11" s="3"/>
+      <x:c r="J11" s="3"/>
+      <x:c r="K11" s="3"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells count="1">
+    <x:mergeCell ref="A1:B1"/>
+  </x:mergeCells>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K7"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11">
+      <x:c r="A1" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D2" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H2" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K2" s="3"/>
+    </x:row>
+    <x:row r="3" spans="1:11">
       <x:c r="A3" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
@@ -899,294 +1933,30 @@
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="3">
-        <x:v>700</x:v>
-      </x:c>
-      <x:c r="B6" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C6" s="3">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D6" s="4">
-        <x:f>B6*C6</x:f>
-      </x:c>
-      <x:c r="E6" s="4">
-        <x:v>1850</x:v>
-      </x:c>
-      <x:c r="F6" s="5">
-        <x:f>+E6/D6</x:f>
-      </x:c>
-      <x:c r="G6" s="4">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H6" s="4">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="I6" s="4">
-        <x:f>+H6-G6</x:f>
-      </x:c>
-      <x:c r="J6" s="5">
-        <x:f>+H6/G6</x:f>
-      </x:c>
+      <x:c r="A6" s="3"/>
+      <x:c r="B6" s="3"/>
+      <x:c r="C6" s="3"/>
+      <x:c r="D6" s="3"/>
+      <x:c r="E6" s="3"/>
+      <x:c r="F6" s="3"/>
+      <x:c r="G6" s="3"/>
+      <x:c r="H6" s="3"/>
+      <x:c r="I6" s="3"/>
+      <x:c r="J6" s="3"/>
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="A7" s="3">
-        <x:v>972</x:v>
-      </x:c>
-      <x:c r="B7" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="3">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D7" s="4">
-        <x:f>B7*C7</x:f>
-      </x:c>
-      <x:c r="E7" s="4">
-        <x:v>2000</x:v>
-      </x:c>
-      <x:c r="F7" s="5">
-        <x:f>+E7/D7</x:f>
-      </x:c>
-      <x:c r="G7" s="4">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H7" s="4">
-        <x:v>55000</x:v>
-      </x:c>
-      <x:c r="I7" s="4">
-        <x:f>+H7-G7</x:f>
-      </x:c>
-      <x:c r="J7" s="5">
-        <x:f>+H7/G7</x:f>
-      </x:c>
+      <x:c r="A7" s="3"/>
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3"/>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3"/>
+      <x:c r="F7" s="3"/>
+      <x:c r="G7" s="3"/>
+      <x:c r="H7" s="3"/>
+      <x:c r="I7" s="3"/>
+      <x:c r="J7" s="3"/>
       <x:c r="K7" s="3"/>
-    </x:row>
-    <x:row r="8" spans="1:11">
-      <x:c r="A8" s="3">
-        <x:v>959</x:v>
-      </x:c>
-      <x:c r="B8" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="3">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="D8" s="4">
-        <x:f>B8*C8</x:f>
-      </x:c>
-      <x:c r="E8" s="4">
-        <x:v>1850</x:v>
-      </x:c>
-      <x:c r="F8" s="5">
-        <x:f>+E8/D8</x:f>
-      </x:c>
-      <x:c r="G8" s="4">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H8" s="4">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="I8" s="4">
-        <x:f>+H8-G8</x:f>
-      </x:c>
-      <x:c r="J8" s="5">
-        <x:f>+H8/G8</x:f>
-      </x:c>
-      <x:c r="K8" s="3"/>
-    </x:row>
-    <x:row r="9" spans="1:11">
-      <x:c r="A9" s="3">
-        <x:v>1201</x:v>
-      </x:c>
-      <x:c r="B9" s="3">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="3">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D9" s="4">
-        <x:f>B9*C9</x:f>
-      </x:c>
-      <x:c r="E9" s="4">
-        <x:v>1020</x:v>
-      </x:c>
-      <x:c r="F9" s="5">
-        <x:f>+E9/D9</x:f>
-      </x:c>
-      <x:c r="G9" s="4">
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="H9" s="4">
-        <x:v>24500</x:v>
-      </x:c>
-      <x:c r="I9" s="4">
-        <x:f>+H9-G9</x:f>
-      </x:c>
-      <x:c r="J9" s="5">
-        <x:f>+H9/G9</x:f>
-      </x:c>
-      <x:c r="K9" s="3"/>
-    </x:row>
-    <x:row r="10" spans="1:11">
-      <x:c r="A10" s="3">
-        <x:v>1305</x:v>
-      </x:c>
-      <x:c r="B10" s="3">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C10" s="3">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D10" s="4">
-        <x:f>B10*C10</x:f>
-      </x:c>
-      <x:c r="E10" s="4">
-        <x:v>1150</x:v>
-      </x:c>
-      <x:c r="F10" s="5">
-        <x:f>+E10/D10</x:f>
-      </x:c>
-      <x:c r="G10" s="4">
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="H10" s="4">
-        <x:v>28800</x:v>
-      </x:c>
-      <x:c r="I10" s="4">
-        <x:f>+H10-G10</x:f>
-      </x:c>
-      <x:c r="J10" s="5">
-        <x:f>+H10/G10</x:f>
-      </x:c>
-      <x:c r="K10" s="3"/>
-    </x:row>
-    <x:row r="11" spans="1:11">
-      <x:c r="A11" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B11" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C11" s="3">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D11" s="4">
-        <x:f>B11*C11</x:f>
-      </x:c>
-      <x:c r="E11" s="4">
-        <x:v>1310</x:v>
-      </x:c>
-      <x:c r="F11" s="5">
-        <x:f>+E11/D11</x:f>
-      </x:c>
-      <x:c r="G11" s="4">
-        <x:v>36000</x:v>
-      </x:c>
-      <x:c r="H11" s="4">
-        <x:v>36500</x:v>
-      </x:c>
-      <x:c r="I11" s="4">
-        <x:f>+H11-G11</x:f>
-      </x:c>
-      <x:c r="J11" s="5">
-        <x:f>+H11/G11</x:f>
-      </x:c>
-      <x:c r="K11" s="3"/>
-    </x:row>
-    <x:row r="12" spans="1:11">
-      <x:c r="A12" s="3">
-        <x:v>640</x:v>
-      </x:c>
-      <x:c r="B12" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C12" s="3">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="D12" s="4">
-        <x:f>B12*C12</x:f>
-      </x:c>
-      <x:c r="E12" s="4">
-        <x:v>1700</x:v>
-      </x:c>
-      <x:c r="F12" s="5">
-        <x:f>+E12/D12</x:f>
-      </x:c>
-      <x:c r="G12" s="4">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="H12" s="4">
-        <x:v>51000</x:v>
-      </x:c>
-      <x:c r="I12" s="4">
-        <x:f>+H12-G12</x:f>
-      </x:c>
-      <x:c r="J12" s="5">
-        <x:f>+H12/G12</x:f>
-      </x:c>
-      <x:c r="K12" s="3"/>
-    </x:row>
-    <x:row r="13" spans="1:11">
-      <x:c r="A13" s="3">
-        <x:v>515</x:v>
-      </x:c>
-      <x:c r="B13" s="3">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="3">
-        <x:v>160</x:v>
-      </x:c>
-      <x:c r="D13" s="4">
-        <x:f>B13*C13</x:f>
-      </x:c>
-      <x:c r="E13" s="4">
-        <x:v>1500</x:v>
-      </x:c>
-      <x:c r="F13" s="5">
-        <x:f>+E13/D13</x:f>
-      </x:c>
-      <x:c r="G13" s="4">
-        <x:v>42000</x:v>
-      </x:c>
-      <x:c r="H13" s="4">
-        <x:v>40100</x:v>
-      </x:c>
-      <x:c r="I13" s="4">
-        <x:f>+H13-G13</x:f>
-      </x:c>
-      <x:c r="J13" s="5">
-        <x:f>+H13/G13</x:f>
-      </x:c>
-      <x:c r="K13" s="3"/>
-    </x:row>
-    <x:row r="14" spans="1:11">
-      <x:c r="A14" s="3"/>
-      <x:c r="B14" s="3"/>
-      <x:c r="C14" s="3"/>
-      <x:c r="D14" s="3"/>
-      <x:c r="E14" s="3"/>
-      <x:c r="F14" s="3"/>
-      <x:c r="G14" s="3"/>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-    </x:row>
-    <x:row r="15" spans="1:11">
-      <x:c r="A15" s="3"/>
-      <x:c r="B15" s="3"/>
-      <x:c r="C15" s="3"/>
-      <x:c r="D15" s="3"/>
-      <x:c r="E15" s="3"/>
-      <x:c r="F15" s="3"/>
-      <x:c r="G15" s="3"/>
-      <x:c r="H15" s="3"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
-      <x:c r="K15" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">

--- a/samples/SanLuong-khach-mau.xlsx
+++ b/samples/SanLuong-khach-mau.xlsx
@@ -72,6 +72,9 @@
     <x:t>BAO TAY XANH</x:t>
   </x:si>
   <x:si>
+    <x:t>TỔNG / 合计</x:t>
+  </x:si>
+  <x:si>
     <x:t>GĂNG TAY TRẮNG</x:t>
   </x:si>
   <x:si>
@@ -88,7 +91,7 @@
     <x:numFmt numFmtId="164" formatCode="#,##0"/>
     <x:numFmt numFmtId="165" formatCode="0%"/>
   </x:numFmts>
-  <x:fonts count="1">
+  <x:fonts count="2">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -96,13 +99,26 @@
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="2">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
     </x:fill>
   </x:fills>
   <x:borders count="2">
@@ -141,7 +157,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="4">
+  <x:cellStyleXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -154,8 +170,17 @@
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="6">
+  <x:cellXfs count="9">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -177,6 +202,18 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="165" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -475,7 +512,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K7"/>
+  <x:dimension ref="A1:K8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -619,16 +656,32 @@
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="3"/>
-      <x:c r="C6" s="3"/>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-      <x:c r="F6" s="3"/>
-      <x:c r="G6" s="3"/>
-      <x:c r="H6" s="3"/>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
+      <x:c r="A6" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="7">
+        <x:f>SUM(D3:D5)</x:f>
+      </x:c>
+      <x:c r="E6" s="7">
+        <x:f>SUM(E3:E5)</x:f>
+      </x:c>
+      <x:c r="F6" s="8">
+        <x:f>IF(D6=0,"",E6/D6)</x:f>
+      </x:c>
+      <x:c r="G6" s="7">
+        <x:f>SUM(G3:G5)</x:f>
+      </x:c>
+      <x:c r="H6" s="7">
+        <x:f>SUM(H3:H5)</x:f>
+      </x:c>
+      <x:c r="I6" s="7">
+        <x:f>SUM(I3:I5)</x:f>
+      </x:c>
+      <x:c r="J6" s="8">
+        <x:f>IF(G6=0,"",H6/G6)</x:f>
+      </x:c>
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -643,6 +696,19 @@
       <x:c r="I7" s="3"/>
       <x:c r="J7" s="3"/>
       <x:c r="K7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="3"/>
+      <x:c r="B8" s="3"/>
+      <x:c r="C8" s="3"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
@@ -661,7 +727,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K7"/>
+  <x:dimension ref="A1:K8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -805,16 +871,32 @@
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="3"/>
-      <x:c r="C6" s="3"/>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-      <x:c r="F6" s="3"/>
-      <x:c r="G6" s="3"/>
-      <x:c r="H6" s="3"/>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
+      <x:c r="A6" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="7">
+        <x:f>SUM(D3:D5)</x:f>
+      </x:c>
+      <x:c r="E6" s="7">
+        <x:f>SUM(E3:E5)</x:f>
+      </x:c>
+      <x:c r="F6" s="8">
+        <x:f>IF(D6=0,"",E6/D6)</x:f>
+      </x:c>
+      <x:c r="G6" s="7">
+        <x:f>SUM(G3:G5)</x:f>
+      </x:c>
+      <x:c r="H6" s="7">
+        <x:f>SUM(H3:H5)</x:f>
+      </x:c>
+      <x:c r="I6" s="7">
+        <x:f>SUM(I3:I5)</x:f>
+      </x:c>
+      <x:c r="J6" s="8">
+        <x:f>IF(G6=0,"",H6/G6)</x:f>
+      </x:c>
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -829,6 +911,19 @@
       <x:c r="I7" s="3"/>
       <x:c r="J7" s="3"/>
       <x:c r="K7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="3"/>
+      <x:c r="B8" s="3"/>
+      <x:c r="C8" s="3"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
@@ -847,7 +942,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K8"/>
+  <x:dimension ref="A1:K9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -1024,16 +1119,32 @@
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="3"/>
-      <x:c r="C7" s="3"/>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3"/>
-      <x:c r="F7" s="3"/>
-      <x:c r="G7" s="3"/>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
+      <x:c r="A7" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="7">
+        <x:f>SUM(D3:D6)</x:f>
+      </x:c>
+      <x:c r="E7" s="7">
+        <x:f>SUM(E3:E6)</x:f>
+      </x:c>
+      <x:c r="F7" s="8">
+        <x:f>IF(D7=0,"",E7/D7)</x:f>
+      </x:c>
+      <x:c r="G7" s="7">
+        <x:f>SUM(G3:G6)</x:f>
+      </x:c>
+      <x:c r="H7" s="7">
+        <x:f>SUM(H3:H6)</x:f>
+      </x:c>
+      <x:c r="I7" s="7">
+        <x:f>SUM(I3:I6)</x:f>
+      </x:c>
+      <x:c r="J7" s="8">
+        <x:f>IF(G7=0,"",H7/G7)</x:f>
+      </x:c>
       <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -1048,6 +1159,19 @@
       <x:c r="I8" s="3"/>
       <x:c r="J8" s="3"/>
       <x:c r="K8" s="3"/>
+    </x:row>
+    <x:row r="9" spans="1:11">
+      <x:c r="A9" s="3"/>
+      <x:c r="B9" s="3"/>
+      <x:c r="C9" s="3"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
+      <x:c r="H9" s="3"/>
+      <x:c r="I9" s="3"/>
+      <x:c r="J9" s="3"/>
+      <x:c r="K9" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
@@ -1066,7 +1190,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K7"/>
+  <x:dimension ref="A1:K8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -1112,7 +1236,7 @@
     </x:row>
     <x:row r="3" spans="1:11">
       <x:c r="A3" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="3">
         <x:v>10</x:v>
@@ -1210,16 +1334,32 @@
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="3"/>
-      <x:c r="C6" s="3"/>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-      <x:c r="F6" s="3"/>
-      <x:c r="G6" s="3"/>
-      <x:c r="H6" s="3"/>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
+      <x:c r="A6" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="7">
+        <x:f>SUM(D3:D5)</x:f>
+      </x:c>
+      <x:c r="E6" s="7">
+        <x:f>SUM(E3:E5)</x:f>
+      </x:c>
+      <x:c r="F6" s="8">
+        <x:f>IF(D6=0,"",E6/D6)</x:f>
+      </x:c>
+      <x:c r="G6" s="7">
+        <x:f>SUM(G3:G5)</x:f>
+      </x:c>
+      <x:c r="H6" s="7">
+        <x:f>SUM(H3:H5)</x:f>
+      </x:c>
+      <x:c r="I6" s="7">
+        <x:f>SUM(I3:I5)</x:f>
+      </x:c>
+      <x:c r="J6" s="8">
+        <x:f>IF(G6=0,"",H6/G6)</x:f>
+      </x:c>
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -1234,6 +1374,19 @@
       <x:c r="I7" s="3"/>
       <x:c r="J7" s="3"/>
       <x:c r="K7" s="3"/>
+    </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="3"/>
+      <x:c r="B8" s="3"/>
+      <x:c r="C8" s="3"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
@@ -1252,7 +1405,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K8"/>
+  <x:dimension ref="A1:K9"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -1429,16 +1582,32 @@
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
-      <x:c r="A7" s="3"/>
-      <x:c r="B7" s="3"/>
-      <x:c r="C7" s="3"/>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3"/>
-      <x:c r="F7" s="3"/>
-      <x:c r="G7" s="3"/>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
+      <x:c r="A7" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="7">
+        <x:f>SUM(D3:D6)</x:f>
+      </x:c>
+      <x:c r="E7" s="7">
+        <x:f>SUM(E3:E6)</x:f>
+      </x:c>
+      <x:c r="F7" s="8">
+        <x:f>IF(D7=0,"",E7/D7)</x:f>
+      </x:c>
+      <x:c r="G7" s="7">
+        <x:f>SUM(G3:G6)</x:f>
+      </x:c>
+      <x:c r="H7" s="7">
+        <x:f>SUM(H3:H6)</x:f>
+      </x:c>
+      <x:c r="I7" s="7">
+        <x:f>SUM(I3:I6)</x:f>
+      </x:c>
+      <x:c r="J7" s="8">
+        <x:f>IF(G7=0,"",H7/G7)</x:f>
+      </x:c>
       <x:c r="K7" s="3"/>
     </x:row>
     <x:row r="8" spans="1:11">
@@ -1453,6 +1622,19 @@
       <x:c r="I8" s="3"/>
       <x:c r="J8" s="3"/>
       <x:c r="K8" s="3"/>
+    </x:row>
+    <x:row r="9" spans="1:11">
+      <x:c r="A9" s="3"/>
+      <x:c r="B9" s="3"/>
+      <x:c r="C9" s="3"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3"/>
+      <x:c r="F9" s="3"/>
+      <x:c r="G9" s="3"/>
+      <x:c r="H9" s="3"/>
+      <x:c r="I9" s="3"/>
+      <x:c r="J9" s="3"/>
+      <x:c r="K9" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
@@ -1471,7 +1653,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K11"/>
+  <x:dimension ref="A1:K12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -1747,16 +1929,32 @@
       <x:c r="K9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:11">
-      <x:c r="A10" s="3"/>
-      <x:c r="B10" s="3"/>
-      <x:c r="C10" s="3"/>
-      <x:c r="D10" s="3"/>
-      <x:c r="E10" s="3"/>
-      <x:c r="F10" s="3"/>
-      <x:c r="G10" s="3"/>
-      <x:c r="H10" s="3"/>
-      <x:c r="I10" s="3"/>
-      <x:c r="J10" s="3"/>
+      <x:c r="A10" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B10" s="6"/>
+      <x:c r="C10" s="6"/>
+      <x:c r="D10" s="7">
+        <x:f>SUM(D3:D9)</x:f>
+      </x:c>
+      <x:c r="E10" s="7">
+        <x:f>SUM(E3:E9)</x:f>
+      </x:c>
+      <x:c r="F10" s="8">
+        <x:f>IF(D10=0,"",E10/D10)</x:f>
+      </x:c>
+      <x:c r="G10" s="7">
+        <x:f>SUM(G3:G9)</x:f>
+      </x:c>
+      <x:c r="H10" s="7">
+        <x:f>SUM(H3:H9)</x:f>
+      </x:c>
+      <x:c r="I10" s="7">
+        <x:f>SUM(I3:I9)</x:f>
+      </x:c>
+      <x:c r="J10" s="8">
+        <x:f>IF(G10=0,"",H10/G10)</x:f>
+      </x:c>
       <x:c r="K10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:11">
@@ -1771,6 +1969,19 @@
       <x:c r="I11" s="3"/>
       <x:c r="J11" s="3"/>
       <x:c r="K11" s="3"/>
+    </x:row>
+    <x:row r="12" spans="1:11">
+      <x:c r="A12" s="3"/>
+      <x:c r="B12" s="3"/>
+      <x:c r="C12" s="3"/>
+      <x:c r="D12" s="3"/>
+      <x:c r="E12" s="3"/>
+      <x:c r="F12" s="3"/>
+      <x:c r="G12" s="3"/>
+      <x:c r="H12" s="3"/>
+      <x:c r="I12" s="3"/>
+      <x:c r="J12" s="3"/>
+      <x:c r="K12" s="3"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
@@ -1789,7 +2000,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:K7"/>
+  <x:dimension ref="A1:K8"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="11" width="16.710625" style="0" customWidth="1"/>
@@ -1797,7 +2008,7 @@
   <x:sheetData>
     <x:row r="1" spans="1:11">
       <x:c r="A1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:11">
@@ -1933,16 +2144,32 @@
       <x:c r="K5" s="3"/>
     </x:row>
     <x:row r="6" spans="1:11">
-      <x:c r="A6" s="3"/>
-      <x:c r="B6" s="3"/>
-      <x:c r="C6" s="3"/>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-      <x:c r="F6" s="3"/>
-      <x:c r="G6" s="3"/>
-      <x:c r="H6" s="3"/>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
+      <x:c r="A6" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B6" s="6"/>
+      <x:c r="C6" s="6"/>
+      <x:c r="D6" s="7">
+        <x:f>SUM(D3:D5)</x:f>
+      </x:c>
+      <x:c r="E6" s="7">
+        <x:f>SUM(E3:E5)</x:f>
+      </x:c>
+      <x:c r="F6" s="8">
+        <x:f>IF(D6=0,"",E6/D6)</x:f>
+      </x:c>
+      <x:c r="G6" s="7">
+        <x:f>SUM(G3:G5)</x:f>
+      </x:c>
+      <x:c r="H6" s="7">
+        <x:f>SUM(H3:H5)</x:f>
+      </x:c>
+      <x:c r="I6" s="7">
+        <x:f>SUM(I3:I5)</x:f>
+      </x:c>
+      <x:c r="J6" s="8">
+        <x:f>IF(G6=0,"",H6/G6)</x:f>
+      </x:c>
       <x:c r="K6" s="3"/>
     </x:row>
     <x:row r="7" spans="1:11">
@@ -1958,6 +2185,19 @@
       <x:c r="J7" s="3"/>
       <x:c r="K7" s="3"/>
     </x:row>
+    <x:row r="8" spans="1:11">
+      <x:c r="A8" s="3"/>
+      <x:c r="B8" s="3"/>
+      <x:c r="C8" s="3"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3"/>
+      <x:c r="F8" s="3"/>
+      <x:c r="G8" s="3"/>
+      <x:c r="H8" s="3"/>
+      <x:c r="I8" s="3"/>
+      <x:c r="J8" s="3"/>
+      <x:c r="K8" s="3"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells count="1">
     <x:mergeCell ref="A1:B1"/>
